--- a/data/trans_orig/P0902-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48963</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55816</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87381</t>
+          <t>88318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424813</t>
+          <t>426392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449703</t>
+          <t>449581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257060</t>
+          <t>259773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280598</t>
+          <t>280888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693076</t>
+          <t>692139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724641</t>
+          <t>726160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69852</t>
+          <t>68572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336569</t>
+          <t>337897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355473</t>
+          <t>355307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326006</t>
+          <t>326425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348344</t>
+          <t>348037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>668947</t>
+          <t>670227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698926</t>
+          <t>698929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53996</t>
+          <t>53068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>22998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488393</t>
+          <t>489321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512311</t>
+          <t>512097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125035</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145631</t>
+          <t>144784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622602</t>
+          <t>620834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652959</t>
+          <t>652655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>107462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147243</t>
+          <t>146797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>71286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105660</t>
+          <t>106926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186035</t>
+          <t>187920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240994</t>
+          <t>242506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1091091</t>
+          <t>1091537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131704</t>
+          <t>1130872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608625</t>
+          <t>607359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643408</t>
+          <t>642999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1711626</t>
+          <t>1710114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1766585</t>
+          <t>1764700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26905</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49340</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69716</t>
+          <t>67609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102956</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99395</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140452</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301215</t>
+          <t>301646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323650</t>
+          <t>323779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>465796</t>
+          <t>467841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499036</t>
+          <t>501143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778855</t>
+          <t>778820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819912</t>
+          <t>818828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194282</t>
+          <t>192822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251077</t>
+          <t>246397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203223</t>
+          <t>203151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258968</t>
+          <t>258892</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293450</t>
+          <t>293620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>997683</t>
+          <t>1002363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1054478</t>
+          <t>1055938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1287992</t>
+          <t>1288068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1343737</t>
+          <t>1343809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240096</t>
+          <t>237248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>302282</t>
+          <t>296922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>454550</t>
+          <t>450980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>535322</t>
+          <t>535524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>706199</t>
+          <t>712378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>809013</t>
+          <t>813197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2967908</t>
+          <t>2973268</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3030094</t>
+          <t>3032942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2842802</t>
+          <t>2842600</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2923574</t>
+          <t>2927144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5839301</t>
+          <t>5835117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5942115</t>
+          <t>5935936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>50691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48073</t>
+          <t>47886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81384</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>398932</t>
+          <t>400544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420547</t>
+          <t>420920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263814</t>
+          <t>263763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287951</t>
+          <t>288389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670281</t>
+          <t>671936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703592</t>
+          <t>703779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31050</t>
+          <t>31109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>50259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62981</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98073</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359764</t>
+          <t>361095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387747</t>
+          <t>387688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287710</t>
+          <t>287752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311860</t>
+          <t>311720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658735</t>
+          <t>658368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>693827</t>
+          <t>693808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105864</t>
+          <t>105211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65079</t>
+          <t>64624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>113991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158634</t>
+          <t>161255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522630</t>
+          <t>523283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>559003</t>
+          <t>560585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193138</t>
+          <t>193593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219499</t>
+          <t>219706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728077</t>
+          <t>725456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>771504</t>
+          <t>772720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126956</t>
+          <t>126921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175726</t>
+          <t>177567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,42 +4417,42 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>116253</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>95990</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>138611</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>15,16%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>116253</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>96297</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>136144</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235199</t>
+          <t>234975</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297936</t>
+          <t>296215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983283</t>
+          <t>981442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1032053</t>
+          <t>1032088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,47 +4525,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>84,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>650404</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>628046</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>670667</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>84,84%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>650404</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>630513</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>670360</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1627731</t>
+          <t>1629452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690468</t>
+          <t>1690692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49287</t>
+          <t>49497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78862</t>
+          <t>81646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>185354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235076</t>
+          <t>235077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244179</t>
+          <t>246295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303774</t>
+          <t>306069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431734</t>
+          <t>428950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461309</t>
+          <t>461099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526446</t>
+          <t>526445</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>578015</t>
+          <t>576168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>968344</t>
+          <t>966049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1027939</t>
+          <t>1025823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226067</t>
+          <t>227350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>284557</t>
+          <t>285315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>236277</t>
+          <t>236721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>293910</t>
+          <t>297504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248731</t>
+          <t>248380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262079</t>
+          <t>261911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822761</t>
+          <t>822003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>881251</t>
+          <t>879968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1080290</t>
+          <t>1076696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1137923</t>
+          <t>1137479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>339424</t>
+          <t>332938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>417399</t>
+          <t>416061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>658442</t>
+          <t>652640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>753140</t>
+          <t>754898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1020803</t>
+          <t>1018041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1142497</t>
+          <t>1138906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3003590</t>
+          <t>3004928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3081565</t>
+          <t>3088051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2793040</t>
+          <t>2791282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2887738</t>
+          <t>2893540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5824672</t>
+          <t>5828263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5946366</t>
+          <t>5949128</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23451</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>46226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52592</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56773</t>
+          <t>55176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90966</t>
+          <t>89347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383053</t>
+          <t>382866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405641</t>
+          <t>405845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294463</t>
+          <t>294027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320739</t>
+          <t>320518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685181</t>
+          <t>686800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>719374</t>
+          <t>720971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73261</t>
+          <t>74054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345410</t>
+          <t>346004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363993</t>
+          <t>363061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321256</t>
+          <t>322423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347212</t>
+          <t>347305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676239</t>
+          <t>675446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707624</t>
+          <t>705616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62024</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>69356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103580</t>
+          <t>104225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459890</t>
+          <t>461666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>486850</t>
+          <t>487934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117002</t>
+          <t>117924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139316</t>
+          <t>140095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584456</t>
+          <t>583811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619375</t>
+          <t>618680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104007</t>
+          <t>102787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144882</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88756</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128453</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203167</t>
+          <t>204594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261935</t>
+          <t>260963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004756</t>
+          <t>1001697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1045631</t>
+          <t>1046851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697423</t>
+          <t>697723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737120</t>
+          <t>737683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1713579</t>
+          <t>1714551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1772347</t>
+          <t>1770920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68666</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103190</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>147677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197653</t>
+          <t>195992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225583</t>
+          <t>229022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>286056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>517516</t>
+          <t>521297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552040</t>
+          <t>553696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540591</t>
+          <t>542252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>587442</t>
+          <t>590567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072941</t>
+          <t>1072894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133367</t>
+          <t>1129928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206630</t>
+          <t>203224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>263098</t>
+          <t>263476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>209017</t>
+          <t>210159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>269623</t>
+          <t>270878</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274636</t>
+          <t>275185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286058</t>
+          <t>285454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>818927</t>
+          <t>818549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>875395</t>
+          <t>878801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1099547</t>
+          <t>1098292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1160153</t>
+          <t>1159011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>282890</t>
+          <t>278894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>350229</t>
+          <t>347406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573960</t>
+          <t>580362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>670247</t>
+          <t>675608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>880848</t>
+          <t>874257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1001279</t>
+          <t>998584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3035493</t>
+          <t>3038316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3106828</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2861349</t>
+          <t>2855988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2957636</t>
+          <t>2951234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5916039</t>
+          <t>5918734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6036470</t>
+          <t>6043061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>53027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67218</t>
+          <t>67211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78951</t>
+          <t>80256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111724</t>
+          <t>113028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452294</t>
+          <t>452185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475589</t>
+          <t>475507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380249</t>
+          <t>380256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403835</t>
+          <t>403566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>840955</t>
+          <t>839651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873728</t>
+          <t>872423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55140</t>
+          <t>54499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>76456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108179</t>
+          <t>107559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397073</t>
+          <t>397714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422637</t>
+          <t>422232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321056</t>
+          <t>320016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341580</t>
+          <t>341436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726614</t>
+          <t>727234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>758226</t>
+          <t>758337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>107374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>40394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150539</t>
+          <t>150006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558461</t>
+          <t>560387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644827</t>
+          <t>644929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118375</t>
+          <t>117959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136619</t>
+          <t>136654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>684132</t>
+          <t>684665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794229</t>
+          <t>794277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139510</t>
+          <t>141166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187496</t>
+          <t>187786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>64175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162754</t>
+          <t>161700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201301</t>
+          <t>190356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331867</t>
+          <t>330051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>845973</t>
+          <t>845683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893959</t>
+          <t>892303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>814799</t>
+          <t>815853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>910062</t>
+          <t>913378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1679155</t>
+          <t>1680971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1809721</t>
+          <t>1820666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69401</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101513</t>
+          <t>100843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149158</t>
+          <t>151101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230423</t>
+          <t>230250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236287</t>
+          <t>231002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317062</t>
+          <t>317317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372442</t>
+          <t>373112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404554</t>
+          <t>404884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>609846</t>
+          <t>610019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691111</t>
+          <t>689168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997162</t>
+          <t>996907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1077937</t>
+          <t>1083222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>168878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>208013</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170304</t>
+          <t>171501</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213081</t>
+          <t>215129</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227594</t>
+          <t>225733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237723</t>
+          <t>237702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>555800</t>
+          <t>553358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594962</t>
+          <t>592493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>788797</t>
+          <t>786749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>831574</t>
+          <t>830377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>307929</t>
+          <t>315032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>448245</t>
+          <t>445517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>539693</t>
+          <t>534597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>711070</t>
+          <t>714978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>910531</t>
+          <t>920120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1136134</t>
+          <t>1137399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2924871</t>
+          <t>2927599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3065187</t>
+          <t>3058084</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2865080</t>
+          <t>2861172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3036457</t>
+          <t>3041553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5813133</t>
+          <t>5811868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6038736</t>
+          <t>6029147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0902-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47384</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>25174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>48422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88318</t>
+          <t>87658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426392</t>
+          <t>425407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449581</t>
+          <t>449495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259773</t>
+          <t>258258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280888</t>
+          <t>281506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692139</t>
+          <t>692799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726160</t>
+          <t>724850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>28654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>39114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68572</t>
+          <t>67448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337897</t>
+          <t>338280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355307</t>
+          <t>356236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326425</t>
+          <t>326464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348037</t>
+          <t>347294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>670227</t>
+          <t>671351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698929</t>
+          <t>699685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53068</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>43702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57516</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>88793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489321</t>
+          <t>488558</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512097</t>
+          <t>512487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124571</t>
+          <t>124080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144784</t>
+          <t>145287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620834</t>
+          <t>621378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652655</t>
+          <t>651427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107462</t>
+          <t>106872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146797</t>
+          <t>147719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106926</t>
+          <t>107037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187920</t>
+          <t>186625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242506</t>
+          <t>243717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1091537</t>
+          <t>1090615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130872</t>
+          <t>1131462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607359</t>
+          <t>607248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642999</t>
+          <t>644172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1710114</t>
+          <t>1708903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1764700</t>
+          <t>1765995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>49507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67609</t>
+          <t>67386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100911</t>
+          <t>102773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100479</t>
+          <t>101054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>143083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301646</t>
+          <t>301048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323779</t>
+          <t>324453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467841</t>
+          <t>465979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501143</t>
+          <t>501366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>778820</t>
+          <t>776224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818828</t>
+          <t>818253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>192822</t>
+          <t>196466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246397</t>
+          <t>248445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203151</t>
+          <t>203643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258892</t>
+          <t>258598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>282009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293620</t>
+          <t>293563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1002363</t>
+          <t>1000315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1055938</t>
+          <t>1052294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1288068</t>
+          <t>1288362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1343809</t>
+          <t>1343317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>237248</t>
+          <t>234884</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296922</t>
+          <t>299219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>450980</t>
+          <t>452844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>535524</t>
+          <t>535240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>712378</t>
+          <t>708638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>813197</t>
+          <t>812618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2973268</t>
+          <t>2970971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3032942</t>
+          <t>3035306</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2842600</t>
+          <t>2842884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2927144</t>
+          <t>2925280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5835117</t>
+          <t>5835696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5935936</t>
+          <t>5939676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26065</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50691</t>
+          <t>49613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>48654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400544</t>
+          <t>399564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420920</t>
+          <t>420519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263763</t>
+          <t>264841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288389</t>
+          <t>289403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>671936</t>
+          <t>670773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>703779</t>
+          <t>703011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57702</t>
+          <t>57252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361095</t>
+          <t>361545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387688</t>
+          <t>387563</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287752</t>
+          <t>287443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311720</t>
+          <t>312567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658368</t>
+          <t>656826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>693808</t>
+          <t>692509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>67022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105211</t>
+          <t>106235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113991</t>
+          <t>113401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161255</t>
+          <t>160074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523283</t>
+          <t>522259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560585</t>
+          <t>561472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193593</t>
+          <t>192832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>219706</t>
+          <t>219330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>725456</t>
+          <t>726637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772720</t>
+          <t>773310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126921</t>
+          <t>126557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177567</t>
+          <t>174448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95990</t>
+          <t>97683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138611</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>234975</t>
+          <t>234241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296215</t>
+          <t>299311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>981442</t>
+          <t>984561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1032088</t>
+          <t>1032452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628046</t>
+          <t>629367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670667</t>
+          <t>668974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1629452</t>
+          <t>1626356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690692</t>
+          <t>1691426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49497</t>
+          <t>48646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81646</t>
+          <t>78116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185354</t>
+          <t>185485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>237193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246295</t>
+          <t>244028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306069</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428950</t>
+          <t>432480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461099</t>
+          <t>461950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>526445</t>
+          <t>524329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>576168</t>
+          <t>576037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>966049</t>
+          <t>970013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025823</t>
+          <t>1028090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227350</t>
+          <t>228400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>285315</t>
+          <t>286162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>236721</t>
+          <t>235982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>297504</t>
+          <t>296189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248380</t>
+          <t>249251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261911</t>
+          <t>261948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822003</t>
+          <t>821156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>879968</t>
+          <t>878918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1076696</t>
+          <t>1078011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1137479</t>
+          <t>1138218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332938</t>
+          <t>339211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>416061</t>
+          <t>417213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>652640</t>
+          <t>655260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>754898</t>
+          <t>755147</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1018041</t>
+          <t>1025365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1138906</t>
+          <t>1147703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3004928</t>
+          <t>3003776</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3088051</t>
+          <t>3081778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2791282</t>
+          <t>2791033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2893540</t>
+          <t>2890920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5828263</t>
+          <t>5819466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5949128</t>
+          <t>5941804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>25958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55176</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89347</t>
+          <t>90705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382866</t>
+          <t>382458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405845</t>
+          <t>406527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294027</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320518</t>
+          <t>321097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>686800</t>
+          <t>685442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>720971</t>
+          <t>720227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49850</t>
+          <t>50575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>42832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74054</t>
+          <t>74556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346004</t>
+          <t>345924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363061</t>
+          <t>363314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322423</t>
+          <t>321698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347305</t>
+          <t>346496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675446</t>
+          <t>674944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705616</t>
+          <t>706668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>60556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69356</t>
+          <t>68303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104225</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461666</t>
+          <t>461358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487934</t>
+          <t>486828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117924</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140095</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583811</t>
+          <t>583558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618680</t>
+          <t>619733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102787</t>
+          <t>102688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147941</t>
+          <t>144974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>88292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128153</t>
+          <t>128566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204594</t>
+          <t>201314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260963</t>
+          <t>259621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1001697</t>
+          <t>1004664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1046851</t>
+          <t>1046950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697723</t>
+          <t>697310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737683</t>
+          <t>737584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1714551</t>
+          <t>1715893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1770920</t>
+          <t>1774200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67010</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147677</t>
+          <t>146264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195992</t>
+          <t>194579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229022</t>
+          <t>228461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286056</t>
+          <t>288792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521297</t>
+          <t>518437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>553696</t>
+          <t>552448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>542252</t>
+          <t>543665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>590567</t>
+          <t>591980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072894</t>
+          <t>1070158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1129928</t>
+          <t>1130489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203224</t>
+          <t>207017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>263476</t>
+          <t>264878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>210159</t>
+          <t>206696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>270878</t>
+          <t>271368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275185</t>
+          <t>275466</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285454</t>
+          <t>286056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>818549</t>
+          <t>817147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>878801</t>
+          <t>875008</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1098292</t>
+          <t>1097802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1159011</t>
+          <t>1162474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>282210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347406</t>
+          <t>352697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>580362</t>
+          <t>579172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>675608</t>
+          <t>676092</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>874257</t>
+          <t>875701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>998584</t>
+          <t>1003565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3038316</t>
+          <t>3033025</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3106828</t>
+          <t>3103512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2855988</t>
+          <t>2855504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2951234</t>
+          <t>2952424</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5918734</t>
+          <t>5913753</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6043061</t>
+          <t>6041617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>31495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>56334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67211</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94832</t>
+          <t>103237</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80256</t>
+          <t>86883</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113028</t>
+          <t>122663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>465296</t>
+          <t>508249</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452185</t>
+          <t>494284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475507</t>
+          <t>519123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>392551</t>
+          <t>427543</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380256</t>
+          <t>414907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403566</t>
+          <t>438228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>857847</t>
+          <t>935792</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>839651</t>
+          <t>916366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872423</t>
+          <t>952146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>56847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>58054</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>47233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91645</t>
+          <t>101054</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76456</t>
+          <t>85578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107559</t>
+          <t>119385</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>411178</t>
+          <t>440212</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397714</t>
+          <t>426365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422232</t>
+          <t>451691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>331971</t>
+          <t>365089</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320016</t>
+          <t>353267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341436</t>
+          <t>375910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>743148</t>
+          <t>805301</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727234</t>
+          <t>786970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>758337</t>
+          <t>820777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63645</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107374</t>
+          <t>83838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48952</t>
+          <t>53554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>109777</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40394</t>
+          <t>93563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150006</t>
+          <t>128650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>604116</t>
+          <t>403905</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560387</t>
+          <t>387281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644929</t>
+          <t>418657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128892</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117959</t>
+          <t>133943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136654</t>
+          <t>154394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>733008</t>
+          <t>548839</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>684665</t>
+          <t>529966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794277</t>
+          <t>565053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667761</t>
+          <t>471119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834671</t>
+          <t>658616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>164201</t>
+          <t>178099</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141166</t>
+          <t>154713</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187786</t>
+          <t>202520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>122799</t>
+          <t>139983</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64175</t>
+          <t>122742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161700</t>
+          <t>159940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>287000</t>
+          <t>318082</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190356</t>
+          <t>289527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330051</t>
+          <t>350124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869268</t>
+          <t>952155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>845683</t>
+          <t>927734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892303</t>
+          <t>975541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>854754</t>
+          <t>720649</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>815853</t>
+          <t>700692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>913378</t>
+          <t>737890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1724022</t>
+          <t>1672804</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1680971</t>
+          <t>1640762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1820666</t>
+          <t>1701359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033469</t>
+          <t>1130254</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033469</t>
+          <t>1130254</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033469</t>
+          <t>1130254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977553</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011022</t>
+          <t>1990886</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011022</t>
+          <t>1990886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011022</t>
+          <t>1990886</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>84954</t>
+          <t>92667</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100843</t>
+          <t>112296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>198702</t>
+          <t>214245</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151101</t>
+          <t>194311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230250</t>
+          <t>233668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>283657</t>
+          <t>306911</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231002</t>
+          <t>280702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317317</t>
+          <t>333736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>389001</t>
+          <t>474193</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373112</t>
+          <t>454564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404884</t>
+          <t>490085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>641567</t>
+          <t>615495</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>610019</t>
+          <t>596072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>689168</t>
+          <t>635429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1030567</t>
+          <t>1089689</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996907</t>
+          <t>1062864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083222</t>
+          <t>1115898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473955</t>
+          <t>566860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840269</t>
+          <t>829740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314224</t>
+          <t>1396600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,22 +10348,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>186685</t>
+          <t>203856</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>168878</t>
+          <t>184156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208013</t>
+          <t>225043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>192777</t>
+          <t>209795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>171501</t>
+          <t>187802</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215129</t>
+          <t>231199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234415</t>
+          <t>231288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225733</t>
+          <t>224408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237702</t>
+          <t>234464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>574686</t>
+          <t>640425</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>553358</t>
+          <t>619238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>592493</t>
+          <t>660125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>809101</t>
+          <t>871714</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>786749</t>
+          <t>850310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>830377</t>
+          <t>893707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>399844</t>
+          <t>429288</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>315032</t>
+          <t>397028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>445517</t>
+          <t>471440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>651730</t>
+          <t>719568</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>534597</t>
+          <t>679142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>714978</t>
+          <t>759848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1051574</t>
+          <t>1148857</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>920120</t>
+          <t>1095388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1137399</t>
+          <t>1210610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2973272</t>
+          <t>3010002</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2927599</t>
+          <t>2967850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3058084</t>
+          <t>3042262</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2924420</t>
+          <t>2914136</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2861172</t>
+          <t>2873856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3041553</t>
+          <t>2954562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5897693</t>
+          <t>5924137</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5811868</t>
+          <t>5862384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6029147</t>
+          <t>5977606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373116</t>
+          <t>3439290</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373116</t>
+          <t>3439290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373116</t>
+          <t>3439290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576150</t>
+          <t>3633704</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6949267</t>
+          <t>7072994</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6949267</t>
+          <t>7072994</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6949267</t>
+          <t>7072994</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
